--- a/templates/datenelement-erhebung.xlsx
+++ b/templates/datenelement-erhebung.xlsx
@@ -208,85 +208,90 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
+        <t>Optionale klinische Kategorie (Befund, Bildgebung, Assessment, …) — Sortier-/Review-Hilfe. Aus der Liste wählen oder leer lassen.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>Versorgungsphase — aus der Liste wählen. 'Andere' → Spalte »Phase_falls_andere« nutzen.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>NSCLC, SCLC, lung_cancer_any oder 'NSCLC,SCLC'. Vorschlag — Freitext erlaubt.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Welcher Werttyp wird erfasst? Laienverständliche Auswahl; das MI-Team mappt auf FHIR-Typen.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Wie oft pro Patient:in? Aus der Liste wählen.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>UCUM-Einheit, falls Zahl/Dosis (z. B. mg, mm, %). Vorschlag — Freitext erlaubt; sonst leer.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Wann/durch welches Ereignis wird erfasst? (z. B. 'bei jeder Vorstellung').</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Erhebungsfrequenz. Vorschlag — Freitext erlaubt (z. B. per-encounter, Q3M).</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Primär verantwortliche Rolle. Vorschlag — Freitext erlaubt. Mehrere Rollen/Systeme: Blatt »Datennutzung«.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Nur falls codierter Begriff: Verbindlichkeit der Codeliste. Im Zweifel leer (MI-Team).</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>Status der Standard-Codierung. Im Zweifel leer lassen (MI-Team).</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Primäres Ziel-Standard-Mapping (z. B. fhir-mii-kds, obds, kbv-mio). Optional; MI-Team ergänzt.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Belegende Leitlinie/Quelle — aus der Liste wählen (Pflicht).</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Kapitel / Empfehlungs-Nr. / Tabelle in der Quelle (Pflicht).</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Empfehlungsgrad lt. Leitlinie (A/B/0/EK/Statement/n/a). Optional.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>Evidenzlevel (1a…4, n/a). Vorschlag — Freitext erlaubt. Optional.</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>Beziehungen zu anderen Elementen, Sensitivitäts-Hinweise, offene Fragen.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Name + Klinik/Fachgesellschaft für Rückfragen. Optional.</t>
       </text>
@@ -887,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -909,8 +914,9 @@
     <col width="24" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -931,90 +937,95 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>Versorgungsphase*</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Phase_falls_andere</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Tumorentität</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Datentyp*</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Häufigkeit*</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Einheit_UCUM</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Wann_erfasst_Trigger*</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Erhebungsfrequenz</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Verantwortliche_Rolle*</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Binding-Stärke</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Standard-Bindungs-Status</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Standard-Mapping_(primär)</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Leitlinien-Quelle*</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Kapitel/Empfehlung/Tabelle*</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>Empfehlungsgrad</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>Evidenzlevel</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>Anmerkungen/Beziehungen</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>Kontakt_für_Rückfragen</t>
         </is>
@@ -1038,82 +1049,87 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
+          <t>Sozialanamnese</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
           <t>Onkologische Nachsorge (kurativ behandelt)</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>NSCLC,SCLC</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Codierter Begriff aus Liste (SNOMED/ICD/LOINC)</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Genau einmal (Pflicht)</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>bei jeder Vorstellung</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>per-encounter</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>Onkolog:in</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>mapped</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>fhir-mii-kds</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>S3-LL Lungenkarzinom</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>Empf. 16.3</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="T2" s="6" t="inlineStr">
         <is>
           <t>2b</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="U2" s="6" t="inlineStr">
         <is>
           <t>BEISPIELZEILE — wird beim Import ignoriert; bitte überschreiben oder löschen.</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr"/>
+      <c r="V2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1123,13 +1139,13 @@
       </c>
       <c r="B3" s="7" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="P3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
       <c r="Q3" s="7" t="n"/>
+      <c r="R3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1139,13 +1155,13 @@
       </c>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-      <c r="P4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
       <c r="Q4" s="7" t="n"/>
+      <c r="R4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1155,13 +1171,13 @@
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="P5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
       <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1171,13 +1187,13 @@
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
       <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1187,13 +1203,13 @@
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1203,13 +1219,13 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
       <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1219,13 +1235,13 @@
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
       <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1235,13 +1251,13 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
       <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1251,13 +1267,13 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
       <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1267,13 +1283,13 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
       <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1283,13 +1299,13 @@
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
       <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1299,13 +1315,13 @@
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
       <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1315,13 +1331,13 @@
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
       <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1331,13 +1347,13 @@
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
       <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1347,13 +1363,13 @@
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
       <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1363,13 +1379,13 @@
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
       <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1379,13 +1395,13 @@
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
       <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1395,13 +1411,13 @@
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
       <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1411,13 +1427,13 @@
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
       <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1427,13 +1443,13 @@
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
       <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1443,13 +1459,13 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="P23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
       <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1459,13 +1475,13 @@
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="P24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
       <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1475,13 +1491,13 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="P25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
       <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1491,13 +1507,13 @@
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="P26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
       <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1507,13 +1523,13 @@
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="P27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
       <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1523,13 +1539,13 @@
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="P28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
       <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1539,13 +1555,13 @@
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
       <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1555,13 +1571,13 @@
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="P30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
       <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1571,13 +1587,13 @@
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="P31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
       <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1587,13 +1603,13 @@
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="P32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
       <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1603,13 +1619,13 @@
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="P33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
       <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -1619,13 +1635,13 @@
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="P34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
       <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1635,13 +1651,13 @@
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="P35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
       <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1651,13 +1667,13 @@
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="P36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
       <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -1667,13 +1683,13 @@
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="P37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
       <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -1683,13 +1699,13 @@
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="P38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
       <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -1699,13 +1715,13 @@
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="L39" s="7" t="n"/>
-      <c r="P39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
       <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -1715,13 +1731,13 @@
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="L40" s="7" t="n"/>
-      <c r="P40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
       <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -1731,13 +1747,13 @@
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="P41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
       <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1747,13 +1763,13 @@
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
-      <c r="L42" s="7" t="n"/>
-      <c r="P42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
       <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1763,13 +1779,13 @@
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="P43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
       <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -1779,13 +1795,13 @@
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
-      <c r="J44" s="7" t="n"/>
-      <c r="L44" s="7" t="n"/>
-      <c r="P44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
       <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -1795,13 +1811,13 @@
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
-      <c r="P45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
       <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -1811,13 +1827,13 @@
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="P46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
       <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -1827,13 +1843,13 @@
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="P47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
       <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -1843,13 +1859,13 @@
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="L48" s="7" t="n"/>
-      <c r="P48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
       <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1859,13 +1875,13 @@
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
-      <c r="P49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
       <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1875,13 +1891,13 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
-      <c r="J50" s="7" t="n"/>
-      <c r="L50" s="7" t="n"/>
-      <c r="P50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
       <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -1891,13 +1907,13 @@
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="P51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
       <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -1907,13 +1923,13 @@
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
-      <c r="J52" s="7" t="n"/>
-      <c r="L52" s="7" t="n"/>
-      <c r="P52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
       <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -1923,13 +1939,13 @@
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="G53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
-      <c r="J53" s="7" t="n"/>
-      <c r="L53" s="7" t="n"/>
-      <c r="P53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
       <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -1939,13 +1955,13 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
-      <c r="J54" s="7" t="n"/>
-      <c r="L54" s="7" t="n"/>
-      <c r="P54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
       <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -1955,13 +1971,13 @@
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
-      <c r="J55" s="7" t="n"/>
-      <c r="L55" s="7" t="n"/>
-      <c r="P55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
       <c r="Q55" s="7" t="n"/>
+      <c r="R55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1971,13 +1987,13 @@
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
-      <c r="L56" s="7" t="n"/>
-      <c r="P56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
       <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1987,13 +2003,13 @@
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
-      <c r="J57" s="7" t="n"/>
-      <c r="L57" s="7" t="n"/>
-      <c r="P57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
       <c r="Q57" s="7" t="n"/>
+      <c r="R57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -2003,13 +2019,13 @@
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
-      <c r="J58" s="7" t="n"/>
-      <c r="L58" s="7" t="n"/>
-      <c r="P58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
       <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -2019,13 +2035,13 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
-      <c r="G59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
-      <c r="J59" s="7" t="n"/>
-      <c r="L59" s="7" t="n"/>
-      <c r="P59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
       <c r="Q59" s="7" t="n"/>
+      <c r="R59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -2035,13 +2051,13 @@
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
-      <c r="J60" s="7" t="n"/>
-      <c r="L60" s="7" t="n"/>
-      <c r="P60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
       <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -2051,13 +2067,13 @@
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-      <c r="P61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
       <c r="Q61" s="7" t="n"/>
+      <c r="R61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -2067,54 +2083,57 @@
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="L62" s="7" t="n"/>
-      <c r="P62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
       <c r="Q62" s="7" t="n"/>
+      <c r="R62" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="14">
     <dataValidation sqref="D2:D62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$A$2:$A$5</formula1>
+      <formula1>=Codelisten!$B$2:$B$18</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$B$2:$B$5</formula1>
+    <dataValidation sqref="E2:E62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$C$2:$C$12</formula1>
+    <dataValidation sqref="G2:G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$C$2:$C$5</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$D$2:$D$5</formula1>
+      <formula1>=Codelisten!$D$2:$D$12</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$O$2:$O$18</formula1>
+    <dataValidation sqref="I2:I62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$P$2:$P$10</formula1>
+    <dataValidation sqref="J2:J62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$P$2:$P$18</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Codelisten!$Q$2:$Q$10</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$E$2:$E$5</formula1>
+    <dataValidation sqref="M2:M62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$R$2:$R$10</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$F$2:$F$5</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$G$2:$G$19</formula1>
+      <formula1>=Codelisten!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$H$2:$H$11</formula1>
+      <formula1>=Codelisten!$H$2:$H$19</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$I$2:$I$7</formula1>
+    <dataValidation sqref="Q2:Q62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$I$2:$I$12</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$R$2:$R$8</formula1>
+    <dataValidation sqref="S2:S62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$S$2:$S$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3174,19 +3193,19 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="C2:C183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$J$2:$J$12</formula1>
+      <formula1>=Codelisten!$K$2:$K$12</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$Q$2:$Q$10</formula1>
+      <formula1>=Codelisten!$R$2:$R$10</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$K$2:$K$12</formula1>
+      <formula1>=Codelisten!$L$2:$L$12</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$L$2:$L$5</formula1>
+      <formula1>=Codelisten!$M$2:$M$5</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$M$2:$M$3</formula1>
+      <formula1>=Codelisten!$N$2:$N$3</formula1>
     </dataValidation>
     <dataValidation sqref="A2:A183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datenelemente!$A$2:$A$62</formula1>
@@ -3897,7 +3916,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="C2:C123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$N$2:$N$13</formula1>
+      <formula1>=Codelisten!$O$2:$O$13</formula1>
     </dataValidation>
     <dataValidation sqref="A2:A123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datenelemente!$A$2:$A$62</formula1>
@@ -3914,27 +3933,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="33" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3945,85 +3965,90 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
+          <t>category_laymen</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
           <t>tumor_entity_multi</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>datatype_laymen</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>cardinality_laymen</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>binding_strength</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>standard_binding_status</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>guideline_source</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>recommendation_grade</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>system_laymen</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>usage_laymen</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>sector_laymen</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>ja_nein</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>terminology_system</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>unit_suggest</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>frequency_suggest</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>role_suggest</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>evidence_levels</t>
         </is>
@@ -4037,85 +4062,90 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Befund</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>NSCLC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Ja/Nein</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Genau einmal (Pflicht)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>mapped</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>obds</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>S3-LL Lungenkarzinom</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Primärverwaltungssystem / Praxis-VS (PVS)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>erfasst / eingegeben</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ambulant</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>snomed-ct</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>per-encounter</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Onkolog:in</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
@@ -4129,85 +4159,90 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bildgebung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>SCLC</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Zahl (ganzzahlig, z. B. Score, Anzahl)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Höchstens einmal (optional)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>extensible</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>no-standard-found</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>gekid-adt</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>S3-LL Palliativmedizin</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Krankenhausinformationssystem (KIS/AIS)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>gelesen / eingesehen</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>stationär</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>loinc</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>mg/d</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ad-hoc</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Hausärzt:in</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
@@ -4221,80 +4256,85 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>lung_cancer_any</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Zahl (mit Dezimalstellen)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Mehrfach möglich, mind. einmal</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>preferred</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>pending-mapping</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>gematik-epa-fhir</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>S3-LL Tabakentwöhnung</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Tumordokumentationssystem</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>aktualisiert / korrigiert</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>sektorenübergreifend</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>icd-10-gm</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>einmalig</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Pflegefachperson</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
@@ -4303,498 +4343,578 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Hausärztliche Versorgung / sektorenübergreifende Basisdaten</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Messwert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NSCLC,SCLC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mehrfach möglich (optional)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>gematik-erezept-fhir</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Onkopedia NSCLC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Klinisches/Epidemiologisches Krebsregister</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>geprüft / freigegeben</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>häuslich / zuhause</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>icd-o-3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Palliativteam</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Andere / neue Phase (rechts benennen)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NSCLC,SCLC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mehrfach möglich (optional)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kontakt/Visite</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Datum + Uhrzeit</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>kbv-mio</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Onkopedia SCLC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Statement</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Labor-/Pathologie-IS (LIS)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>übermittelt / ausgetauscht</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>icf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Tumorboard / MDT</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Versorgungsplanung</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Zeitraum (von–bis)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fhir-mii-kds</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OCP Lung (AU)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>gematik-erezept-fhir</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Onkopedia NSCLC</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>EK</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Klinisches/Epidemiologisches Krebsregister</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>geprüft / freigegeben</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>häuslich / zuhause</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>icd-o-3</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Palliativteam</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Datum + Uhrzeit</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>kbv-mio</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Onkopedia SCLC</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Statement</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Labor-/Pathologie-IS (LIS)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>übermittelt / ausgetauscht</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>icf</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Tumorboard / MDT</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zeitraum (von–bis)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>fhir-mii-kds</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OCP Lung (AU)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Radiologie (RIS/PACS)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>gespeichert / archiviert</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Q3M</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Tumordokumentar:in</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mitbetreuung</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Codierter Begriff aus Liste (SNOMED/ICD/LOINC)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fhir-isik</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AG LONKO / Survivorship</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Elektronische Patientenakte (ePA)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>abgeleitet / berechnet</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>kdl</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>/min</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Q6M</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Radiolog:in</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Radiologie (RIS/PACS)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>gespeichert / archiviert</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ops</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Q3M</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tumordokumentar:in</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Codierter Begriff aus Liste (SNOMED/ICD/LOINC)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>fhir-isik</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AG LONKO / Survivorship</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Elektronische Patientenakte (ePA)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>abgeleitet / berechnet</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>kdl</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>/min</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Q6M</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Radiolog:in</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prozedur</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Freitext (kurz)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>fhir-r4-base</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>ESMO</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Patientenportal / PRO-App</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Forschung / Sekundärnutzung</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>atc</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>mo</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Q12M</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Patholog:in</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Freitext (lang)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>fhir-genomics</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>ASCO</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Forschungs-DWH / DIZ / FDPG</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>im Patientenportal angezeigt</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>ucum</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Q3M-Y1-Y2;Q6M-Y3-Y5</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Patient:in (Selbsteinschätzung)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sozialanamnese</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Dosis/Menge mit Einheit (z. B. mg)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>mcode</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Expert:innen-Erhebung MiHUB</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Vernetzungs-/Kooperationsplattform</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>durch Patient:in selbst erfasst</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>hl7-v3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dokument</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Verweis auf Dokument/Befund</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>openehr-archetype</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>andere</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Vernetzungs-/Kooperationsplattform</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>durch Patient:in selbst erfasst</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>hl7-v3</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Verweis auf Dokument/Befund</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>openehr-archetype</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Sonstiges (bitte System benennen)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>meddra</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Laborbefund</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>omop-cdm</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>local-no-standard-binding</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Punkte</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PROM (Selbsteinschätzung)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>cdisc-sdtm</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>mmHg</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="G15" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Medikation</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>hl7-v2</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>µmol/L</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="G16" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Versorgungskontext</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>dicom-sr</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>U/L</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="G17" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stammdaten</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>hl7-cda</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Gy</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="G18" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Administrativ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>ihe-xds</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>other</t>
         </is>

--- a/templates/datenelement-erhebung.xlsx
+++ b/templates/datenelement-erhebung.xlsx
@@ -2097,7 +2097,7 @@
       <formula1>=Codelisten!$B$2:$B$18</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$A$2:$A$6</formula1>
+      <formula1>=Codelisten!$A$2:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Codelisten!$C$2:$C$5</formula1>
@@ -2127,7 +2127,7 @@
       <formula1>=Codelisten!$H$2:$H$19</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
-      <formula1>=Codelisten!$I$2:$I$12</formula1>
+      <formula1>=Codelisten!$I$2:$I$14</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$J$2:$J$7</formula1>
@@ -4057,7 +4057,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Onkologische Nachsorge (kurativ behandelt)</t>
+          <t>Krebsfrüherkennung / LDCT-Screening</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4154,7 +4154,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Verlaufsbeobachtung / Surveillance (unter Systemtherapie)</t>
+          <t>Onkologische Nachsorge (kurativ behandelt)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Palliativversorgung</t>
+          <t>Verlaufsbeobachtung / Surveillance (unter Systemtherapie)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hausärztliche Versorgung / sektorenübergreifende Basisdaten</t>
+          <t>Palliativversorgung</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4435,71 +4435,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Hausärztliche Versorgung / sektorenübergreifende Basisdaten</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kontakt/Visite</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Datum + Uhrzeit</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>kbv-mio</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Onkopedia SCLC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Statement</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Labor-/Pathologie-IS (LIS)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>übermittelt / ausgetauscht</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>icf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Tumorboard / MDT</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Andere / neue Phase (rechts benennen)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kontakt/Visite</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Datum + Uhrzeit</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>kbv-mio</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Onkopedia SCLC</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Statement</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Labor-/Pathologie-IS (LIS)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>übermittelt / ausgetauscht</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>icf</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Tumorboard / MDT</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
       <c r="B7" t="inlineStr">
         <is>
           <t>Versorgungsplanung</t>
@@ -4782,7 +4787,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>andere</t>
+          <t>LuKrFrühErkV</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4817,6 +4822,11 @@
           <t>omop-cdm</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>G-BA KFE-RL</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>local-no-standard-binding</t>
@@ -4837,6 +4847,11 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>cdisc-sdtm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>andere</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
